--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -459,12 +459,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-26, 2026-03-30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-25, 2026-03-30</t>
         </is>
       </c>
     </row>
@@ -474,16 +474,8 @@
           <t>SAONA</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,12 +485,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-21, 2026-02-25</t>
+          <t>2026-03-02, 2026-03-06, 2026-03-16, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
     </row>

--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -436,20 +436,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BELLATERRA AREIA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+          <t>BELATERRA AREIA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-24, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BELLATERRA PIETRA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>BELATERRA PIETRA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,11 +513,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BELLATERRA TEMPUS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>BELATERRA TEMPUS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-12, 2026-03-19, 2026-03-21, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-07, 2026-03-12, 2026-03-20, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -509,8 +533,16 @@
           <t>BAIKAL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
